--- a/TomaInventarioWEB/Plantillas/Plantilla_Producto.xlsx
+++ b/TomaInventarioWEB/Plantillas/Plantilla_Producto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Carlos Figueroa\Proyectos 2024\Toma Inventarios\Fuente\TomaInventario\TomaInventarioWEB_IQFARMA\TomaInventarioWEB\Plantillas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Desktop\Documentos\TomaDeInventario - Web\TomaInventario-GitHub\TomaInventarioWEB\Plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A21BE49-E264-4634-AEAD-C971838B2EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9A974A-5804-4ACA-B09F-C44DE87A9A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1125" yWindow="0" windowWidth="20880" windowHeight="11835" xr2:uid="{67C386F5-27F8-4261-BF4C-5F77FEEA6F00}"/>
+    <workbookView xWindow="28755" yWindow="4470" windowWidth="25530" windowHeight="14160" xr2:uid="{67C386F5-27F8-4261-BF4C-5F77FEEA6F00}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,13 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>COD_PRODUCTO</t>
-  </si>
-  <si>
-    <t>DSC_PRODUCTO</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>CPU MC9090K</t>
   </si>
@@ -48,9 +42,6 @@
     <t>21-61358-01</t>
   </si>
   <si>
-    <t>COD 1</t>
-  </si>
-  <si>
     <t>CÓDIGO</t>
   </si>
   <si>
@@ -60,36 +51,32 @@
     <t>VALOR</t>
   </si>
   <si>
-    <t>En caso no se desee agregar una unidad de medida, dejar el espacio en blanco</t>
-  </si>
-  <si>
-    <t>LISTA DE UNIDADES DE MEDIDA</t>
-  </si>
-  <si>
-    <t>COD_UNIDAD_MEDIDA</t>
+    <t>UND</t>
+  </si>
+  <si>
+    <t>Unidad</t>
+  </si>
+  <si>
+    <t>LISTA DE UNIDADES DE MEDIDA (REFERENCIAL)</t>
+  </si>
+  <si>
+    <t>CÓDIGO DE PRODUCTO</t>
+  </si>
+  <si>
+    <t>DESCRIPCIÓN PRODUCTO</t>
+  </si>
+  <si>
+    <t>CÓDIGO DE UNIDAD MEDIDA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -104,25 +91,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1" tint="0.499984740745262"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -134,18 +113,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
+        <fgColor theme="4" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0070C0"/>
+        <fgColor theme="7" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -165,12 +144,19 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -182,7 +168,9 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -190,9 +178,13 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -201,25 +193,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -535,67 +533,67 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F00432-D8BC-42FC-B196-DFEFADEB5870}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.5703125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="34" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="80.140625" customWidth="1"/>
-    <col min="3" max="3" width="22.85546875" customWidth="1"/>
+    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.7109375" customWidth="1"/>
     <col min="7" max="7" width="46.85546875" customWidth="1"/>
     <col min="8" max="8" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G1" s="8"/>
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="F3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="5">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F3" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="F2:H2"/>
+  <mergeCells count="1">
+    <mergeCell ref="F1:H1"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="AVISO!" error="No puede Ingresar más de 20 caracteres en esta celda" sqref="A1:A1048576" xr:uid="{5634BA0D-829E-488E-AF26-19ABDA1CB07C}">
@@ -604,7 +602,7 @@
     <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="AVISO!" error="No puede ingresar más de 200 caracteres en esta celda" sqref="B1:B1048576 C1:C2" xr:uid="{B078B425-461D-4E96-AE7F-85715965BEFD}">
       <formula1>200</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H5:H1048576" xr:uid="{6AFC20A7-5642-4747-A22E-B9079618770F}">
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6:H1048576 H3" xr:uid="{6AFC20A7-5642-4747-A22E-B9079618770F}">
       <formula1>1</formula1>
     </dataValidation>
   </dataValidations>

--- a/TomaInventarioWEB/Plantillas/Plantilla_Producto.xlsx
+++ b/TomaInventarioWEB/Plantillas/Plantilla_Producto.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Desktop\Documentos\TomaDeInventario - Web\TomaInventario-GitHub\TomaInventarioWEB\Plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B9A974A-5804-4ACA-B09F-C44DE87A9A0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70048BB1-1388-428E-BF96-9DCA34810A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28755" yWindow="4470" windowWidth="25530" windowHeight="14160" xr2:uid="{67C386F5-27F8-4261-BF4C-5F77FEEA6F00}"/>
+    <workbookView xWindow="0" yWindow="1320" windowWidth="26085" windowHeight="14160" xr2:uid="{67C386F5-27F8-4261-BF4C-5F77FEEA6F00}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>CPU MC9090K</t>
   </si>
@@ -54,19 +54,16 @@
     <t>UND</t>
   </si>
   <si>
-    <t>Unidad</t>
-  </si>
-  <si>
     <t>LISTA DE UNIDADES DE MEDIDA (REFERENCIAL)</t>
   </si>
   <si>
-    <t>CÓDIGO DE PRODUCTO</t>
-  </si>
-  <si>
-    <t>DESCRIPCIÓN PRODUCTO</t>
-  </si>
-  <si>
-    <t>CÓDIGO DE UNIDAD MEDIDA</t>
+    <t>COD_PRODUCTO</t>
+  </si>
+  <si>
+    <t>DSC_PRODUCTO</t>
+  </si>
+  <si>
+    <t>COD_UNIDAD_MEDIDA</t>
   </si>
 </sst>
 </file>
@@ -201,22 +198,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -539,26 +536,26 @@
     <col min="1" max="1" width="34" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="80.140625" customWidth="1"/>
     <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" customWidth="1"/>
-    <col min="7" max="7" width="46.85546875" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" style="7" customWidth="1"/>
+    <col min="7" max="7" width="46.85546875" style="7" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="7" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="8"/>
-      <c r="H1" s="9"/>
+      <c r="F1" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="9"/>
+      <c r="H1" s="10"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -580,17 +577,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="F3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="5">
-        <v>1</v>
-      </c>
-    </row>
+    <row r="3" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="F1:H1"/>

--- a/TomaInventarioWEB/Plantillas/Plantilla_Producto.xlsx
+++ b/TomaInventarioWEB/Plantillas/Plantilla_Producto.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Desktop\Documentos\TomaDeInventario - Web\TomaInventario-GitHub\TomaInventarioWEB\Plantillas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dmspe\Downloads\Toma_Inventario-GitHub\TomaInventarioWEB\TomaInventarioWEB\Plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70048BB1-1388-428E-BF96-9DCA34810A0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E8042B-3695-42F5-9FE4-4D162DB33A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1320" windowWidth="26085" windowHeight="14160" xr2:uid="{67C386F5-27F8-4261-BF4C-5F77FEEA6F00}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{67C386F5-27F8-4261-BF4C-5F77FEEA6F00}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>CPU MC9090K</t>
   </si>
@@ -64,13 +64,22 @@
   </si>
   <si>
     <t>COD_UNIDAD_MEDIDA</t>
+  </si>
+  <si>
+    <t>PRECIO_COSTO</t>
+  </si>
+  <si>
+    <t>COD_MONEDA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,6 +108,14 @@
       <color theme="0"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -190,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -206,6 +223,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -530,18 +554,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F00432-D8BC-42FC-B196-DFEFADEB5870}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="80.140625" customWidth="1"/>
     <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.7109375" style="7" customWidth="1"/>
-    <col min="7" max="7" width="46.85546875" style="7" customWidth="1"/>
+    <col min="4" max="4" width="34.85546875" customWidth="1"/>
+    <col min="5" max="5" width="36.42578125" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="7" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="7" customWidth="1"/>
     <col min="8" max="8" width="12.7109375" style="7" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" customWidth="1"/>
+    <col min="10" max="10" width="21.140625" customWidth="1"/>
+    <col min="11" max="11" width="22.7109375" customWidth="1"/>
+    <col min="12" max="12" width="24.42578125" customWidth="1"/>
+    <col min="13" max="13" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>7</v>
       </c>
@@ -551,13 +582,19 @@
       <c r="C1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="D1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="9"/>
-      <c r="H1" s="10"/>
+      <c r="L1" s="12"/>
+      <c r="M1" s="13"/>
     </row>
-    <row r="2" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -567,26 +604,39 @@
       <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="D2" s="10">
+        <v>1730.2</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="K2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="L2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="M2" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="K8" s="8"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="K1:M1"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="AVISO!" error="No puede Ingresar más de 20 caracteres en esta celda" sqref="A1:A1048576" xr:uid="{5634BA0D-829E-488E-AF26-19ABDA1CB07C}">
       <formula1>20</formula1>
     </dataValidation>
-    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="AVISO!" error="No puede ingresar más de 200 caracteres en esta celda" sqref="B1:B1048576 C1:C2" xr:uid="{B078B425-461D-4E96-AE7F-85715965BEFD}">
+    <dataValidation type="textLength" operator="lessThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="AVISO!" error="No puede ingresar más de 200 caracteres en esta celda" sqref="B1:B1048576 C1:E2" xr:uid="{B078B425-461D-4E96-AE7F-85715965BEFD}">
       <formula1>200</formula1>
     </dataValidation>
     <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H6:H1048576 H3" xr:uid="{6AFC20A7-5642-4747-A22E-B9079618770F}">

--- a/TomaInventarioWEB/Plantillas/Plantilla_Producto.xlsx
+++ b/TomaInventarioWEB/Plantillas/Plantilla_Producto.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dmspe\Downloads\Toma_Inventario-GitHub\TomaInventarioWEB\TomaInventarioWEB\Plantillas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\User\Desktop\Documentos\TomaDeInventario - Web\TomaInventario-GitHub\TomaInventarioWEB\Plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9E8042B-3695-42F5-9FE4-4D162DB33A63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD14985-969C-4229-BE34-954AE8C5AC76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{67C386F5-27F8-4261-BF4C-5F77FEEA6F00}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{67C386F5-27F8-4261-BF4C-5F77FEEA6F00}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,44 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Fiorella Carbajal</author>
+  </authors>
+  <commentList>
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{8817A1D5-E497-4140-96B1-FA987BB38F6A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Esta columna es OPCIONAL</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{A06E6618-720A-4E04-AD3F-DBB213B0BC40}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Esta columna es OPCIONAL</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
@@ -72,14 +110,14 @@
     <t>COD_MONEDA</t>
   </si>
   <si>
-    <t>USD</t>
+    <t>PE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,6 +155,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -209,9 +254,6 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -224,12 +266,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -238,6 +283,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -553,80 +604,80 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F00432-D8BC-42FC-B196-DFEFADEB5870}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51F00432-D8BC-42FC-B196-DFEFADEB5870}">
   <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="34" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="80.140625" customWidth="1"/>
-    <col min="3" max="3" width="40.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="34.85546875" customWidth="1"/>
-    <col min="5" max="5" width="36.42578125" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" style="7" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="7" customWidth="1"/>
-    <col min="8" max="8" width="12.7109375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="40.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.85546875" style="13" customWidth="1"/>
+    <col min="5" max="5" width="36.42578125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="4" customWidth="1"/>
+    <col min="7" max="7" width="13.140625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="12.7109375" style="4" customWidth="1"/>
     <col min="9" max="9" width="11.85546875" customWidth="1"/>
     <col min="10" max="10" width="21.140625" customWidth="1"/>
-    <col min="11" max="11" width="22.7109375" customWidth="1"/>
-    <col min="12" max="12" width="24.42578125" customWidth="1"/>
-    <col min="13" max="13" width="19.140625" customWidth="1"/>
+    <col min="11" max="11" width="22.7109375" style="4" customWidth="1"/>
+    <col min="12" max="12" width="24.42578125" style="4" customWidth="1"/>
+    <col min="13" max="13" width="19.140625" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="12"/>
-      <c r="M1" s="13"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="11"/>
     </row>
     <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
+      <c r="D2" s="12">
         <v>1730.2</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="K8" s="8"/>
+      <c r="K8" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -645,5 +696,6 @@
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>